--- a/LIBRARY MANAGEMENT SYSTEM TEST CASES.xlsx
+++ b/LIBRARY MANAGEMENT SYSTEM TEST CASES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="8_{4EC6CA6C-951A-4423-970D-9EF3946F9AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{167F628E-FFC8-4E18-9290-E0B9894F8518}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{4EC6CA6C-951A-4423-970D-9EF3946F9AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F60200-E650-4DEC-BAA7-DEFD03A1662B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{D4FA9ED5-C48F-432D-89D9-82E781F80FD8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D4FA9ED5-C48F-432D-89D9-82E781F80FD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -902,9 +902,6 @@
     <t>CHANGES_CLEARED_AND_REDIRECTED</t>
   </si>
   <si>
-    <t>1.1 UPDATE USER</t>
-  </si>
-  <si>
     <t>LOGIN</t>
   </si>
   <si>
@@ -1158,6 +1155,9 @@
   </si>
   <si>
     <t>SUCCESS_LOGIN_AFTER_FAILURE</t>
+  </si>
+  <si>
+    <t>1.2 UPDATE USER</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1593,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>288</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3610,7 +3610,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3618,7 +3618,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3626,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3679,10 +3679,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -3691,7 +3691,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>32</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>240</v>
@@ -3725,16 +3725,16 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>98</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>242</v>
@@ -3757,7 +3757,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>57</v>
@@ -3771,19 +3771,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>106</v>
@@ -3794,33 +3794,33 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>43</v>
@@ -3840,19 +3840,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>135</v>
@@ -3863,16 +3863,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>57</v>
@@ -3886,65 +3886,65 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>130</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
@@ -3955,19 +3955,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>58</v>
@@ -3978,19 +3978,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
@@ -4001,19 +4001,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>203</v>
@@ -4024,19 +4024,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>203</v>
@@ -4047,19 +4047,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>203</v>
@@ -4070,19 +4070,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>203</v>
@@ -4093,19 +4093,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>203</v>
@@ -4116,19 +4116,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>203</v>
@@ -4139,19 +4139,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
@@ -4162,19 +4162,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
@@ -4185,19 +4185,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>

--- a/LIBRARY MANAGEMENT SYSTEM TEST CASES.xlsx
+++ b/LIBRARY MANAGEMENT SYSTEM TEST CASES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="8_{4EC6CA6C-951A-4423-970D-9EF3946F9AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F60200-E650-4DEC-BAA7-DEFD03A1662B}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="8_{4EC6CA6C-951A-4423-970D-9EF3946F9AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1549716-4380-49CA-B79F-02E5D56E9F68}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D4FA9ED5-C48F-432D-89D9-82E781F80FD8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{D4FA9ED5-C48F-432D-89D9-82E781F80FD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="377">
   <si>
     <t>APPLICATION NAME</t>
   </si>
@@ -1158,6 +1158,15 @@
   </si>
   <si>
     <t>1.2 UPDATE USER</t>
+  </si>
+  <si>
+    <t>REVIEWER_NAME</t>
+  </si>
+  <si>
+    <t>REVIEWED_DATE</t>
+  </si>
+  <si>
+    <t>APPROVED_DATE</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1237,6 +1246,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1558,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BBF85-8074-4A84-A5EE-1900274F2F20}">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
@@ -2443,6 +2455,21 @@
         <v>287</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -2458,7 +2485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BA7397-356E-4E13-9248-9643CED17202}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -3563,13 +3590,25 @@
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="2"/>
+      <c r="A56" s="7" t="s">
+        <v>374</v>
+      </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="7" t="s">
+        <v>376</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3582,7 +3621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC19ED4-3DA9-4D02-8ABA-57ADC861BFC5}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -4206,6 +4245,21 @@
         <v>47</v>
       </c>
     </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F10" r:id="rId1" display="mailto:abc@gmail.com" xr:uid="{C0E777BB-F7E5-4AFD-93D2-836371F9FF6C}"/>
